--- a/exports/VOLTAS_full_report.xlsx
+++ b/exports/VOLTAS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>3.81</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1251.35</v>
+        <v>1235.35</v>
       </c>
       <c r="I2" t="n">
         <v>1244.241583861056</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.62</v>
+        <v>-1.89</v>
       </c>
       <c r="L2" t="n">
-        <v>1.57</v>
+        <v>4.18</v>
       </c>
       <c r="M2" t="n">
-        <v>0.35</v>
+        <v>1.71</v>
       </c>
       <c r="N2" t="n">
-        <v>1.59</v>
+        <v>4.83</v>
       </c>
       <c r="O2" t="n">
         <v>-1.26</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>4.18</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44609.55208333334</v>
+        <v>44610.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>1223.35</v>
+        <v>1251.25</v>
       </c>
       <c r="I3" t="n">
         <v>1250.049144498305</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K3" t="n">
-        <v>0.97</v>
+        <v>-1.29</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="M3" t="n">
         <v>0.6899999999999999</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>8</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44623.55208333334</v>
+        <v>44624.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>1197.3</v>
+        <v>1171.35</v>
       </c>
       <c r="I4" t="n">
         <v>1180.144778506254</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.31</v>
+        <v>-6.39</v>
       </c>
       <c r="L4" t="n">
-        <v>5.53</v>
+        <v>7.92</v>
       </c>
       <c r="M4" t="n">
         <v>2.45</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>8.83</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44635.55208333334</v>
+        <v>44636.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1210</v>
+        <v>1272.7</v>
       </c>
       <c r="I5" t="n">
         <v>1227.52778390726</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.3</v>
+        <v>-8.65</v>
       </c>
       <c r="L5" t="n">
-        <v>4.52</v>
+        <v>10.09</v>
       </c>
       <c r="M5" t="n">
         <v>3.07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.9</v>
+        <v>5.29</v>
       </c>
       <c r="O5" t="n">
         <v>-1.96</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>9.34</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1302</v>
+        <v>1246</v>
       </c>
       <c r="I6" t="n">
         <v>1250.289218594431</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="L6" t="n">
         <v>4.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.12</v>
+        <v>1.87</v>
       </c>
       <c r="N6" t="n">
-        <v>2.15</v>
+        <v>4.24</v>
       </c>
       <c r="O6" t="n">
         <v>5.29</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.88</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44711.38541666666</v>
+        <v>44711.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>1032.9</v>
+        <v>1040.9</v>
       </c>
       <c r="I7" t="n">
         <v>1035.880459859276</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K7" t="n">
-        <v>17.1</v>
+        <v>16.46</v>
       </c>
       <c r="L7" t="n">
         <v>4.25</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.09</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44727.55208333334</v>
+        <v>44728.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>991</v>
+        <v>969</v>
       </c>
       <c r="I8" t="n">
         <v>978.7674162980148</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.79</v>
+        <v>-6.91</v>
       </c>
       <c r="L8" t="n">
         <v>7.8</v>
@@ -897,7 +992,7 @@
         <v>1.61</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>3.63</v>
       </c>
       <c r="O8" t="n">
         <v>2.96</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>8.57</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44757.55208333334</v>
+        <v>44760.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>985</v>
+        <v>1034.9</v>
       </c>
       <c r="I9" t="n">
         <v>1002.722175737487</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.65</v>
+        <v>-6.8</v>
       </c>
       <c r="L9" t="n">
-        <v>4.18</v>
+        <v>7.32</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.38</v>
+        <v>4.96</v>
       </c>
       <c r="O9" t="n">
         <v>-3.63</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.38</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44764.38541666666</v>
+        <v>44764.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>1007.5</v>
+        <v>998.8</v>
       </c>
       <c r="I10" t="n">
         <v>998.9644486479325</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.65</v>
+        <v>-3.49</v>
       </c>
       <c r="L10" t="n">
         <v>4.19</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>5.72</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44785.55208333334</v>
+        <v>44789.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1009.9</v>
+        <v>1017.2</v>
       </c>
       <c r="I11" t="n">
         <v>1011.456955311766</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>21</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.11</v>
+        <v>-1.84</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6</v>
+        <v>3.87</v>
       </c>
       <c r="M11" t="n">
-        <v>0.89</v>
+        <v>1.4</v>
       </c>
       <c r="N11" t="n">
         <v>2.93</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>4.11</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1014.7</v>
+        <v>986.1</v>
       </c>
       <c r="I12" t="n">
         <v>996.3978875296631</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.25</v>
+        <v>-3.06</v>
       </c>
       <c r="L12" t="n">
-        <v>0.73</v>
+        <v>3.76</v>
       </c>
       <c r="M12" t="n">
-        <v>-0</v>
+        <v>0.46</v>
       </c>
       <c r="N12" t="n">
-        <v>2.96</v>
+        <v>3.63</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.7</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44866.38541666666</v>
+        <v>44866.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>894.6</v>
+        <v>907.5</v>
       </c>
       <c r="I13" t="n">
         <v>897.8594519690523</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>71</v>
+        <v>71.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>9.279999999999999</v>
+        <v>7.97</v>
       </c>
       <c r="L13" t="n">
         <v>3.01</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>5.06</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44867.55208333334</v>
+        <v>44868.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>910</v>
+        <v>866</v>
       </c>
       <c r="I14" t="n">
         <v>866.6612104163729</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>0.28</v>
+        <v>-4.57</v>
       </c>
       <c r="L14" t="n">
-        <v>2.14</v>
+        <v>4.68</v>
       </c>
       <c r="M14" t="n">
         <v>1.49</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
         <v>3.48</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.65</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44893.38541666666</v>
+        <v>44893.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>837.15</v>
+        <v>840</v>
       </c>
       <c r="I15" t="n">
         <v>838.7083074781681</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>4.97</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>3.5</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44915.55208333334</v>
+        <v>44916.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>829</v>
+        <v>821.35</v>
       </c>
       <c r="I16" t="n">
         <v>826.3679862793389</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.31</v>
+        <v>-2.22</v>
       </c>
       <c r="L16" t="n">
         <v>3.1</v>
@@ -1353,7 +1544,7 @@
         <v>0.45</v>
       </c>
       <c r="N16" t="n">
-        <v>1.81</v>
+        <v>2.23</v>
       </c>
       <c r="O16" t="n">
         <v>1.33</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>4.94</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44935.55208333334</v>
+        <v>44936.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>817.2</v>
+        <v>819</v>
       </c>
       <c r="I17" t="n">
         <v>818.4527969814453</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
       <c r="L17" t="n">
         <v>2.02</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>3.99</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44944.38541666666</v>
+        <v>44944.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>804.5</v>
+        <v>800.65</v>
       </c>
       <c r="I18" t="n">
         <v>801.1518278773331</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.77</v>
+        <v>-2.24</v>
       </c>
       <c r="L18" t="n">
         <v>2.31</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>3.43</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44956.38541666666</v>
+        <v>44956.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>769.65</v>
+        <v>778</v>
       </c>
       <c r="I19" t="n">
         <v>775.9695737754315</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
-        <v>3.87</v>
+        <v>2.83</v>
       </c>
       <c r="L19" t="n">
         <v>0.61</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.26</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>881.25</v>
+        <v>871</v>
       </c>
       <c r="I20" t="n">
         <v>878.8441185379658</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>42</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="K20" t="n">
-        <v>13.27</v>
+        <v>11.95</v>
       </c>
       <c r="L20" t="n">
         <v>1.21</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>6.17</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45034.55208333334</v>
+        <v>45035.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>835.4</v>
+        <v>848.9</v>
       </c>
       <c r="I21" t="n">
         <v>844.9493262171984</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K21" t="n">
-        <v>4.09</v>
+        <v>2.54</v>
       </c>
       <c r="L21" t="n">
         <v>3.65</v>
@@ -1638,7 +1889,7 @@
         <v>2.13</v>
       </c>
       <c r="N21" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="O21" t="n">
         <v>-1.9</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>4.85</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45042.55208333334</v>
+        <v>45043.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>860</v>
+        <v>815.45</v>
       </c>
       <c r="I22" t="n">
         <v>830.5543017758437</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
-        <v>1.31</v>
+        <v>-3.94</v>
       </c>
       <c r="L22" t="n">
-        <v>1.97</v>
+        <v>4.25</v>
       </c>
       <c r="M22" t="n">
-        <v>0.12</v>
+        <v>3.43</v>
       </c>
       <c r="N22" t="n">
-        <v>1.15</v>
+        <v>6.22</v>
       </c>
       <c r="O22" t="n">
         <v>1.9</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.26</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>815</v>
+        <v>825.05</v>
       </c>
       <c r="I23" t="n">
         <v>820.8232769962179</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06</v>
+        <v>-1.18</v>
       </c>
       <c r="L23" t="n">
         <v>3.87</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>3.44</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45082.55208333334</v>
+        <v>45083.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>823.65</v>
+        <v>800.5</v>
       </c>
       <c r="I24" t="n">
         <v>801.7711112935878</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.17</v>
+        <v>-2.98</v>
       </c>
       <c r="L24" t="n">
-        <v>1.17</v>
+        <v>4.08</v>
       </c>
       <c r="M24" t="n">
         <v>0.47</v>
       </c>
       <c r="N24" t="n">
-        <v>0.82</v>
+        <v>2.52</v>
       </c>
       <c r="O24" t="n">
         <v>1.35</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>4.61</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45090.55208333334</v>
+        <v>45091.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>805.35</v>
+        <v>822.5</v>
       </c>
       <c r="I25" t="n">
         <v>811.3941720774383</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.61</v>
+        <v>-2.75</v>
       </c>
       <c r="L25" t="n">
-        <v>2.94</v>
+        <v>3.31</v>
       </c>
       <c r="M25" t="n">
         <v>0.76</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>5.39</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45098.55208333334</v>
+        <v>45099.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>786.5</v>
+        <v>780.2</v>
       </c>
       <c r="I26" t="n">
         <v>783.5658379219941</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.38</v>
+        <v>-5.14</v>
       </c>
       <c r="L26" t="n">
-        <v>4.8</v>
+        <v>5.34</v>
       </c>
       <c r="M26" t="n">
-        <v>-0</v>
+        <v>0.06</v>
       </c>
       <c r="N26" t="n">
         <v>1.97</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>4.05</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45125.55208333334</v>
+        <v>45126.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>765.9</v>
+        <v>778.2</v>
       </c>
       <c r="I27" t="n">
         <v>771.5067022659317</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K27" t="n">
-        <v>1.83</v>
+        <v>0.26</v>
       </c>
       <c r="L27" t="n">
-        <v>1.13</v>
+        <v>1.62</v>
       </c>
       <c r="M27" t="n">
         <v>0.65</v>
       </c>
       <c r="N27" t="n">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="O27" t="n">
         <v>-0.58</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>3.99</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45156.38541666666</v>
+        <v>45156.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>813</v>
+        <v>809.3</v>
       </c>
       <c r="I28" t="n">
         <v>811.7353130514722</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>30</v>
+        <v>30.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>4.47</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
         <v>2.73</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>5.21</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45166.55208333334</v>
+        <v>45167.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>829</v>
+        <v>849.05</v>
       </c>
       <c r="I29" t="n">
         <v>846.9060000852425</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.43</v>
+        <v>-4.91</v>
       </c>
       <c r="L29" t="n">
-        <v>3.93</v>
+        <v>5.24</v>
       </c>
       <c r="M29" t="n">
         <v>0.34</v>
       </c>
       <c r="N29" t="n">
-        <v>1.61</v>
+        <v>2.53</v>
       </c>
       <c r="O29" t="n">
         <v>-1.74</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.27</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45181.38541666666</v>
+        <v>45181.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>877.6</v>
+        <v>875</v>
       </c>
       <c r="I30" t="n">
         <v>875.8427998871847</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>3.36</v>
+        <v>3.06</v>
       </c>
       <c r="L30" t="n">
         <v>2.54</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>4.61</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45250.55208333334</v>
+        <v>45251.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>831.95</v>
+        <v>844.8</v>
       </c>
       <c r="I31" t="n">
         <v>844.0428110001333</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>69</v>
+        <v>69.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>4.92</v>
+        <v>3.45</v>
       </c>
       <c r="L31" t="n">
         <v>3.54</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>4.37</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1028</v>
+        <v>1009.35</v>
       </c>
       <c r="I32" t="n">
         <v>1013.349743594277</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K32" t="n">
-        <v>21.69</v>
+        <v>19.48</v>
       </c>
       <c r="L32" t="n">
         <v>3.98</v>
@@ -2265,7 +2648,7 @@
         <v>1.25</v>
       </c>
       <c r="N32" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="O32" t="n">
         <v>1.63</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>6.68</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45321.55208333334</v>
+        <v>45322.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1020</v>
+        <v>1089.3</v>
       </c>
       <c r="I33" t="n">
         <v>1067.009833456582</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.06</v>
+        <v>-7.92</v>
       </c>
       <c r="L33" t="n">
-        <v>4.72</v>
+        <v>8.58</v>
       </c>
       <c r="M33" t="n">
         <v>0.77</v>
       </c>
       <c r="N33" t="n">
-        <v>3.25</v>
+        <v>6.76</v>
       </c>
       <c r="O33" t="n">
         <v>-2.24</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>13.03</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45356.55208333334</v>
+        <v>45357.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1072</v>
+        <v>1051.35</v>
       </c>
       <c r="I34" t="n">
         <v>1054.237112195399</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.59</v>
+        <v>-3.48</v>
       </c>
       <c r="L34" t="n">
         <v>9.109999999999999</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>8.43</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45373.55208333334</v>
+        <v>45377.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1068.7</v>
+        <v>1112.7</v>
       </c>
       <c r="I35" t="n">
         <v>1109.362695650341</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.65</v>
+        <v>-5.84</v>
       </c>
       <c r="L35" t="n">
-        <v>4.24</v>
+        <v>6.15</v>
       </c>
       <c r="M35" t="n">
         <v>1.48</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.75</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1450.8</v>
+        <v>1393.6</v>
       </c>
       <c r="I36" t="n">
         <v>1423.065519282991</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K36" t="n">
-        <v>30.39</v>
+        <v>25.24</v>
       </c>
       <c r="L36" t="n">
         <v>4.76</v>
@@ -2493,7 +2924,7 @@
         <v>1.25</v>
       </c>
       <c r="N36" t="n">
-        <v>2.52</v>
+        <v>4.69</v>
       </c>
       <c r="O36" t="n">
         <v>2.96</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.49</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45435.55208333334</v>
+        <v>45436.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1348.3</v>
+        <v>1380.9</v>
       </c>
       <c r="I37" t="n">
         <v>1360.018921471213</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K37" t="n">
-        <v>3.25</v>
+        <v>0.91</v>
       </c>
       <c r="L37" t="n">
         <v>4.94</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.64</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45474.55208333334</v>
+        <v>45475.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1446</v>
+        <v>1420.8</v>
       </c>
       <c r="I38" t="n">
         <v>1439.198901335775</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K38" t="n">
-        <v>4.71</v>
+        <v>2.89</v>
       </c>
       <c r="L38" t="n">
         <v>10.24</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>6.85</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45484.55208333334</v>
+        <v>45485.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1515.95</v>
+        <v>1520.5</v>
       </c>
       <c r="I39" t="n">
         <v>1516.822545418386</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.7</v>
+        <v>-7.02</v>
       </c>
       <c r="L39" t="n">
-        <v>6.77</v>
+        <v>7.19</v>
       </c>
       <c r="M39" t="n">
         <v>0.8100000000000001</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>4.92</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45492.38541666666</v>
+        <v>45492.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>1475.65</v>
+        <v>1470.25</v>
       </c>
       <c r="I40" t="n">
         <v>1472.234427527369</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.95</v>
+        <v>-3.3</v>
       </c>
       <c r="L40" t="n">
-        <v>3.19</v>
+        <v>3.32</v>
       </c>
       <c r="M40" t="n">
         <v>0.11</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>4.85</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45503.38541666666</v>
+        <v>45503.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>1538.3</v>
+        <v>1543.95</v>
       </c>
       <c r="I41" t="n">
         <v>1541.594763139364</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.63</v>
+        <v>-5.01</v>
       </c>
       <c r="L41" t="n">
         <v>6.09</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>5.73</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1487.9</v>
+        <v>1447.1</v>
       </c>
       <c r="I42" t="n">
         <v>1462.246735107991</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.63</v>
+        <v>-6.27</v>
       </c>
       <c r="L42" t="n">
-        <v>4.02</v>
+        <v>7.19</v>
       </c>
       <c r="M42" t="n">
         <v>1.04</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>6.57</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45513.55208333334</v>
+        <v>45516.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1432.3</v>
+        <v>1575.55</v>
       </c>
       <c r="I43" t="n">
         <v>1517.2497781115</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K43" t="n">
-        <v>1.02</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>4.52</v>
+        <v>10.43</v>
       </c>
       <c r="M43" t="n">
-        <v>1.37</v>
+        <v>4.73</v>
       </c>
       <c r="N43" t="n">
-        <v>0.83</v>
+        <v>10.52</v>
       </c>
       <c r="O43" t="n">
         <v>-2.55</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.97</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1849.7</v>
+        <v>1815.15</v>
       </c>
       <c r="I44" t="n">
         <v>1838.940924698027</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K44" t="n">
-        <v>17.4</v>
+        <v>15.21</v>
       </c>
       <c r="L44" t="n">
         <v>7.13</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>6.19</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45580.55208333334</v>
+        <v>45581.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1814</v>
+        <v>1875.6</v>
       </c>
       <c r="I45" t="n">
         <v>1862.732815061072</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K45" t="n">
-        <v>0.06</v>
+        <v>-3.33</v>
       </c>
       <c r="L45" t="n">
-        <v>2.67</v>
+        <v>4.78</v>
       </c>
       <c r="M45" t="n">
-        <v>0.48</v>
+        <v>1.44</v>
       </c>
       <c r="N45" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="O45" t="n">
         <v>-2.15</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>6.58</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45589.55208333334</v>
+        <v>45590.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1794.95</v>
+        <v>1760.05</v>
       </c>
       <c r="I46" t="n">
         <v>1776.133855742214</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.3</v>
+        <v>-6.16</v>
       </c>
       <c r="L46" t="n">
-        <v>5.57</v>
+        <v>7.29</v>
       </c>
       <c r="M46" t="n">
         <v>0.38</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.58</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45603.38541666666</v>
+        <v>45603.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>1746.8</v>
+        <v>1771.9</v>
       </c>
       <c r="I47" t="n">
         <v>1761.837905798346</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>0.75</v>
+        <v>-0.67</v>
       </c>
       <c r="L47" t="n">
         <v>2.44</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>7.72</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45621.38541666666</v>
+        <v>45621.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>1675.6</v>
+        <v>1637</v>
       </c>
       <c r="I48" t="n">
         <v>1651.792190944743</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>17.83333333333333</v>
+        <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.43</v>
+        <v>-7.61</v>
       </c>
       <c r="L48" t="n">
-        <v>7.01</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M48" t="n">
         <v>0.02</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>7.72</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45632.55208333334</v>
+        <v>45635.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1714</v>
+        <v>1760.7</v>
       </c>
       <c r="I49" t="n">
         <v>1743.549887426403</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.7</v>
+        <v>-7.56</v>
       </c>
       <c r="L49" t="n">
-        <v>5.42</v>
+        <v>7.76</v>
       </c>
       <c r="M49" t="n">
         <v>2.02</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>6.58</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1744</v>
+        <v>1711.1</v>
       </c>
       <c r="I50" t="n">
         <v>1735.830434119012</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.95</v>
+        <v>-2.82</v>
       </c>
       <c r="L50" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="M50" t="n">
         <v>0.36</v>
       </c>
       <c r="N50" t="n">
-        <v>2.26</v>
+        <v>3.43</v>
       </c>
       <c r="O50" t="n">
         <v>2.86</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.18</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45656.55208333334</v>
+        <v>45657.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1736.15</v>
+        <v>1774.65</v>
       </c>
       <c r="I51" t="n">
         <v>1756.371540220872</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.46</v>
+        <v>-3.71</v>
       </c>
       <c r="L51" t="n">
         <v>5.2</v>
@@ -3348,7 +3959,7 @@
         <v>0.27</v>
       </c>
       <c r="N51" t="n">
-        <v>2.09</v>
+        <v>3.29</v>
       </c>
       <c r="O51" t="n">
         <v>-3.43</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>7.12</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1780.15</v>
+        <v>1713.45</v>
       </c>
       <c r="I52" t="n">
         <v>1730.072018724339</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K52" t="n">
-        <v>0.31</v>
+        <v>-3.45</v>
       </c>
       <c r="L52" t="n">
-        <v>2.43</v>
+        <v>3.8</v>
       </c>
       <c r="M52" t="n">
         <v>0.44</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45691.38541666666</v>
+        <v>45691.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>1379.7</v>
+        <v>1405</v>
       </c>
       <c r="I53" t="n">
         <v>1397.643786997835</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>19.48</v>
+        <v>18</v>
       </c>
       <c r="L53" t="n">
         <v>3.85</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>14.93</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45701.55208333334</v>
+        <v>45702.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1248</v>
+        <v>1215.7</v>
       </c>
       <c r="I54" t="n">
         <v>1230.084169239675</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>-11.17</v>
+        <v>-13.47</v>
       </c>
       <c r="L54" t="n">
-        <v>11.35</v>
+        <v>13.72</v>
       </c>
       <c r="M54" t="n">
         <v>1.64</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>12.41</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45716.55208333334</v>
+        <v>45719.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1322</v>
+        <v>1363.85</v>
       </c>
       <c r="I55" t="n">
         <v>1335.88075895828</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K55" t="n">
-        <v>-8.74</v>
+        <v>-12.19</v>
       </c>
       <c r="L55" t="n">
-        <v>9.859999999999999</v>
+        <v>12.94</v>
       </c>
       <c r="M55" t="n">
-        <v>0.48</v>
+        <v>1.9</v>
       </c>
       <c r="N55" t="n">
         <v>4.8</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>8.85</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45744.55208333334</v>
+        <v>45748.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1461</v>
+        <v>1363.9</v>
       </c>
       <c r="I56" t="n">
         <v>1408.528560250373</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K56" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>3.06</v>
       </c>
       <c r="M56" t="n">
-        <v>0.88</v>
+        <v>2.12</v>
       </c>
       <c r="N56" t="n">
-        <v>3.31</v>
+        <v>7.71</v>
       </c>
       <c r="O56" t="n">
         <v>3.44</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45814.55208333334</v>
+        <v>45817.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1271</v>
+        <v>1291.6</v>
       </c>
       <c r="I57" t="n">
         <v>1271.221618348326</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>66.16666666666667</v>
+        <v>69</v>
       </c>
       <c r="K57" t="n">
-        <v>6.81</v>
+        <v>5.3</v>
       </c>
       <c r="L57" t="n">
         <v>4.85</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>3.98</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45827.38541666666</v>
+        <v>45827.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>1265.9</v>
+        <v>1260</v>
       </c>
       <c r="I58" t="n">
         <v>1260.001754698411</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.99</v>
+        <v>-2.45</v>
       </c>
       <c r="L58" t="n">
-        <v>2.33</v>
+        <v>2.83</v>
       </c>
       <c r="M58" t="n">
         <v>2.01</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>5.73</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45838.55208333334</v>
+        <v>45839.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1315</v>
+        <v>1329.2</v>
       </c>
       <c r="I59" t="n">
         <v>1327.965801325648</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.37</v>
+        <v>-5.49</v>
       </c>
       <c r="L59" t="n">
         <v>6.42</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.11</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45862.38541666666</v>
+        <v>45862.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>1352.8</v>
+        <v>1343.5</v>
       </c>
       <c r="I60" t="n">
         <v>1346.189140320197</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>1.78</v>
+        <v>1.08</v>
       </c>
       <c r="L60" t="n">
         <v>1.26</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>3.9</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1270</v>
+        <v>1363.1</v>
       </c>
       <c r="I61" t="n">
         <v>1311.139966800402</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>21</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>5.47</v>
+        <v>-1.46</v>
       </c>
       <c r="L61" t="n">
-        <v>0.78</v>
+        <v>4.37</v>
       </c>
       <c r="M61" t="n">
-        <v>0.5</v>
+        <v>5.35</v>
       </c>
       <c r="N61" t="n">
-        <v>2.53</v>
+        <v>6.2</v>
       </c>
       <c r="O61" t="n">
         <v>-1.65</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.73</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45922.55208333334</v>
+        <v>45923.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1376</v>
+        <v>1368.6</v>
       </c>
       <c r="I62" t="n">
         <v>1372.548439126978</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K62" t="n">
-        <v>0.95</v>
+        <v>0.4</v>
       </c>
       <c r="L62" t="n">
         <v>2.72</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>4.64</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45939.55208333334</v>
+        <v>45940.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1377.3</v>
+        <v>1424.7</v>
       </c>
       <c r="I63" t="n">
         <v>1404.088794073651</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.64</v>
+        <v>-4.1</v>
       </c>
       <c r="L63" t="n">
-        <v>1.93</v>
+        <v>5.04</v>
       </c>
       <c r="M63" t="n">
-        <v>0.34</v>
+        <v>1.58</v>
       </c>
       <c r="N63" t="n">
         <v>3.55</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>5.86</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45961.55208333334</v>
+        <v>45964.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1383.6</v>
+        <v>1356.8</v>
       </c>
       <c r="I64" t="n">
         <v>1383.091644592191</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.88</v>
+        <v>-4.77</v>
       </c>
       <c r="L64" t="n">
-        <v>4.14</v>
+        <v>4.96</v>
       </c>
       <c r="M64" t="n">
         <v>0.9399999999999999</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>6.18</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45978.55208333334</v>
+        <v>45979.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1376.8</v>
+        <v>1393</v>
       </c>
       <c r="I65" t="n">
         <v>1385.346213127669</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.47</v>
+        <v>-2.67</v>
       </c>
       <c r="L65" t="n">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="M65" t="n">
         <v>0.14</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>7.49</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45993.55208333334</v>
+        <v>45994.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1352</v>
+        <v>1342</v>
       </c>
       <c r="I66" t="n">
         <v>1343.487793435456</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.94</v>
+        <v>-3.66</v>
       </c>
       <c r="L66" t="n">
-        <v>3.67</v>
+        <v>4.09</v>
       </c>
       <c r="M66" t="n">
         <v>0.87</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>6.5</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46003.55208333334</v>
+        <v>46006.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1376</v>
+        <v>1384.4</v>
       </c>
       <c r="I67" t="n">
         <v>1376.767465968075</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.53</v>
+        <v>-3.16</v>
       </c>
       <c r="L67" t="n">
-        <v>2.81</v>
+        <v>3.17</v>
       </c>
       <c r="M67" t="n">
         <v>0.22</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>4.79</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46035.55208333334</v>
+        <v>46036.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1454.5</v>
+        <v>1435.7</v>
       </c>
       <c r="I68" t="n">
         <v>1436.059930179146</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K68" t="n">
-        <v>5.06</v>
+        <v>3.71</v>
       </c>
       <c r="L68" t="n">
         <v>2.94</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>5.69</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46050.38541666666</v>
+        <v>46050.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>1346.5</v>
+        <v>1379</v>
       </c>
       <c r="I69" t="n">
         <v>1375.674439613149</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K69" t="n">
-        <v>6.21</v>
+        <v>3.95</v>
       </c>
       <c r="L69" t="n">
         <v>1.62</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>8.44</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>1500</v>
+        <v>1446.3</v>
       </c>
       <c r="I70" t="n">
         <v>1485.622427941599</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>33</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K70" t="n">
-        <v>8.77</v>
+        <v>4.88</v>
       </c>
       <c r="L70" t="n">
         <v>7.9</v>
@@ -4431,7 +5270,7 @@
         <v>2.34</v>
       </c>
       <c r="N70" t="n">
-        <v>3.69</v>
+        <v>4.27</v>
       </c>
       <c r="O70" t="n">
         <v>2.99</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>7.9</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46106.38541666666</v>
+        <v>46106.55208333334</v>
       </c>
       <c r="H71" t="n">
-        <v>1357.4</v>
+        <v>1379.9</v>
       </c>
       <c r="I71" t="n">
         <v>1369.279592841704</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K71" t="n">
-        <v>6.15</v>
+        <v>4.59</v>
       </c>
       <c r="L71" t="n">
         <v>4.39</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46113.38541666666</v>
+        <v>46113.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>1250.9</v>
+        <v>1242.8</v>
       </c>
       <c r="I72" t="n">
         <v>1250.355664136558</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K72" t="n">
-        <v>-9.35</v>
+        <v>-9.94</v>
       </c>
       <c r="L72" t="n">
-        <v>10.09</v>
+        <v>11.99</v>
       </c>
       <c r="M72" t="n">
         <v>2.29</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>9.77</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46122.55208333334</v>
+        <v>46125.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>1311.4</v>
+        <v>1356.5</v>
       </c>
       <c r="I73" t="n">
         <v>1328.869242256997</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K73" t="n">
-        <v>-5.52</v>
+        <v>-9.15</v>
       </c>
       <c r="L73" t="n">
-        <v>6.13</v>
+        <v>9.35</v>
       </c>
       <c r="M73" t="n">
         <v>2.54</v>
       </c>
       <c r="N73" t="n">
-        <v>3.77</v>
+        <v>4.16</v>
       </c>
       <c r="O73" t="n">
         <v>-2.91</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>11.86</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46146.55208333334</v>
+        <v>46147.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>1452.4</v>
+        <v>1391.5</v>
       </c>
       <c r="I74" t="n">
         <v>1417.469186612004</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K74" t="n">
-        <v>7.07</v>
+        <v>2.58</v>
       </c>
       <c r="L74" t="n">
         <v>6.25</v>
@@ -4659,7 +5546,7 @@
         <v>1.94</v>
       </c>
       <c r="N74" t="n">
-        <v>2.79</v>
+        <v>6.02</v>
       </c>
       <c r="O74" t="n">
         <v>4.16</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>10.18</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46182.55208333334</v>
+        <v>46183.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>1304</v>
+        <v>1311.5</v>
       </c>
       <c r="I75" t="n">
         <v>1305.116498955451</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K75" t="n">
-        <v>6.29</v>
+        <v>5.75</v>
       </c>
       <c r="L75" t="n">
         <v>4.42</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>7.43</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46198.55208333334</v>
+        <v>46202.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>1304.7</v>
+        <v>1288.1</v>
       </c>
       <c r="I76" t="n">
         <v>1292.542113857057</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.52</v>
+        <v>-1.78</v>
       </c>
       <c r="L76" t="n">
         <v>3.01</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>6.65</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46213.55208333334</v>
+        <v>46216.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>1287.9</v>
+        <v>1336</v>
       </c>
       <c r="I77" t="n">
         <v>1329.376490673193</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K77" t="n">
-        <v>0.02</v>
+        <v>-3.72</v>
       </c>
       <c r="L77" t="n">
-        <v>1.45</v>
+        <v>4.33</v>
       </c>
       <c r="M77" t="n">
         <v>0.88</v>
       </c>
       <c r="N77" t="n">
-        <v>1.49</v>
+        <v>4.95</v>
       </c>
       <c r="O77" t="n">
         <v>-0.12</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>7.85</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46225.38541666666</v>
+        <v>46225.55208333334</v>
       </c>
       <c r="H78" t="n">
-        <v>1313.9</v>
+        <v>1308.6</v>
       </c>
       <c r="I78" t="n">
         <v>1310.890386004382</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K78" t="n">
-        <v>-1.65</v>
+        <v>-2.05</v>
       </c>
       <c r="L78" t="n">
         <v>4.69</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,14 @@
       <c r="Q79" t="n">
         <v>133</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7049,7 +8004,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.2</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="6">
@@ -7059,7 +8014,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.2</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="7">
@@ -7069,7 +8024,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>71</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="8">
@@ -7079,7 +8034,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -7089,7 +8044,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -7099,7 +8054,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39.4</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="11">
@@ -7109,7 +8064,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
@@ -7119,7 +8074,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -7129,7 +8084,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>81.8</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -7139,7 +8094,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.42</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="15">
@@ -7149,7 +8104,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.55</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -7159,7 +8114,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.29</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="17">
@@ -7169,7 +8124,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.39</v>
+        <v>25.24</v>
       </c>
     </row>
     <row r="18">
@@ -7179,7 +8134,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.4</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="19">
@@ -7189,7 +8144,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.06</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="20">
@@ -7199,7 +8154,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.87</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="21">
@@ -7209,7 +8164,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.35</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="22">
@@ -7219,7 +8174,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -7229,7 +8184,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -7239,7 +8194,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="25">
@@ -7249,7 +8204,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.21</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="26">
@@ -7259,7 +8214,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="27">
@@ -7269,7 +8224,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.44</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="28">
@@ -7279,7 +8234,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
